--- a/lab-standards/BASIS-lab-standard.xlsx
+++ b/lab-standards/BASIS-lab-standard.xlsx
@@ -559,6 +559,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -574,6 +578,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -643,7 +651,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -666,7 +676,9 @@
       <c r="C17" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -689,7 +701,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -712,7 +726,9 @@
       <c r="C19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -734,7 +750,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -757,7 +775,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -780,7 +800,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -926,6 +948,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -938,6 +964,10 @@
           <t>Classroom cum workshop – 500 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1007,7 +1037,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
       </c>
@@ -1029,7 +1061,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -1051,7 +1085,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -1074,7 +1110,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -1097,7 +1135,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1119,7 +1159,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1141,7 +1183,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1163,7 +1207,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1185,7 +1231,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -1207,7 +1255,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -1229,7 +1279,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -1251,7 +1303,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -1273,7 +1327,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -1295,7 +1351,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -1441,6 +1499,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1456,6 +1518,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1525,7 +1591,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -1547,7 +1615,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -1693,6 +1763,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1708,6 +1782,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1777,7 +1855,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -1799,7 +1879,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
